--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="259">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -485,6 +485,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -674,6 +677,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -684,10 +690,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -700,6 +721,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -707,6 +737,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -714,6 +747,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -726,6 +762,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1108,7 +1150,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -3529,7 +3571,9 @@
       <c r="K24" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L24" s="2"/>
+      <c r="L24" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3600,10 +3644,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3637,7 +3681,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -3659,7 +3703,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -3677,7 +3721,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3697,10 +3741,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3734,7 +3778,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -3756,7 +3800,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -3774,7 +3818,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3794,10 +3838,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3811,7 +3855,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -3823,10 +3867,10 @@
         <v>95</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3877,7 +3921,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3897,10 +3941,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3914,7 +3958,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -3923,13 +3967,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3980,7 +4024,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4000,10 +4044,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4101,10 +4145,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4133,7 +4177,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4145,7 +4189,7 @@
         <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>74</v>
@@ -4184,7 +4228,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4204,17 +4248,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>75</v>
@@ -4236,7 +4280,7 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4248,7 +4292,7 @@
         <v>74</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>74</v>
@@ -4287,7 +4331,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4307,17 +4351,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4339,7 +4383,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4351,7 +4395,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -4390,7 +4434,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4410,17 +4454,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4442,7 +4486,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4493,7 +4537,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4513,17 +4557,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>75</v>
@@ -4545,7 +4589,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4557,7 +4601,7 @@
         <v>74</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>74</v>
@@ -4596,7 +4640,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4616,10 +4660,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4642,11 +4686,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4697,7 +4741,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4717,10 +4761,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4747,7 +4791,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4798,7 +4842,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4818,17 +4862,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -4846,11 +4890,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4901,7 +4945,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4921,17 +4965,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -4949,11 +4993,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5004,7 +5048,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5024,17 +5068,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5052,11 +5096,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5107,7 +5151,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5127,10 +5171,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5144,7 +5188,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5153,16 +5197,18 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5210,7 +5256,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5230,10 +5276,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5247,7 +5293,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5256,15 +5302,17 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>74</v>
@@ -5313,7 +5361,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5333,10 +5381,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5359,12 +5407,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L42" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>74</v>
       </c>
@@ -5412,7 +5464,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5432,10 +5484,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5460,10 +5512,14 @@
       <c r="K43" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L43" s="2"/>
+      <c r="L43" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>74</v>
       </c>
@@ -5491,7 +5547,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5509,7 +5565,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5529,10 +5585,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5555,12 +5611,18 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L44" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>74</v>
       </c>
@@ -5608,7 +5670,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5628,10 +5690,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5654,12 +5716,14 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -5707,7 +5771,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5727,10 +5791,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5753,12 +5817,14 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -5806,7 +5872,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5826,10 +5892,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5852,7 +5918,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -5905,7 +5971,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -5925,10 +5991,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5951,12 +6017,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>74</v>
       </c>
@@ -6004,7 +6074,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6024,10 +6094,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6125,10 +6195,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6226,10 +6296,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6327,10 +6397,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6428,10 +6498,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6531,10 +6601,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6634,10 +6704,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6737,10 +6807,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6840,10 +6910,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6941,10 +7011,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6971,7 +7041,7 @@
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -6980,7 +7050,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>74</v>
@@ -7022,7 +7092,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7042,10 +7112,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7079,7 +7149,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>74</v>
@@ -7121,7 +7191,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7141,10 +7211,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7167,7 +7237,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7220,7 +7290,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-demande-examen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
